--- a/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/Data-Catalog/sneakerpark_data_catalog.xlsx
+++ b/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/Data-Catalog/sneakerpark_data_catalog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be4ab9aaf12c5868/Documents/Github/Udacity-Master-Artificial-Intelligence/udacity-ai-masters/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be4ab9aaf12c5868/Documents/Github/Udacity-Master-Artificial-Intelligence/udacity-ai-masters/Modules/03-Data-Architect/projects/Project 4 - SneakerPark Data Governance/report/Data-Catalog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="8_{A062A1EE-BF8D-41F0-9655-A80E3764D7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BCA54A8-FDCA-488F-A06C-AED9459CFF11}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="8_{A062A1EE-BF8D-41F0-9655-A80E3764D7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C43B570B-CC76-4A95-95AF-E775F0F8AB46}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="250">
   <si>
     <t>Entity</t>
   </si>
@@ -792,15 +792,6 @@
     <t>Convention</t>
   </si>
   <si>
-    <t>Naming Case</t>
-  </si>
-  <si>
-    <t>All Tables must be named using Camel Case</t>
-  </si>
-  <si>
-    <t>ApartmentBuildings</t>
-  </si>
-  <si>
     <t>Business Term</t>
   </si>
   <si>
@@ -808,15 +799,6 @@
   </si>
   <si>
     <t>Term Synonyms</t>
-  </si>
-  <si>
-    <t>Apartment</t>
-  </si>
-  <si>
-    <t>A room or a group of related rooms, among similar sets in one building, designed for use as a dwelling.</t>
-  </si>
-  <si>
-    <t>Flat, Crib, Place, Residence, Suite, Condo</t>
   </si>
   <si>
     <t>Michael</t>
@@ -1326,7 +1308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1395,11 +1377,9 @@
     <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1690,7 +1670,7 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -1711,7 +1691,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I2" s="2">
         <v>1001</v>
@@ -1723,15 +1703,15 @@
         <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>14</v>
@@ -1752,10 +1732,10 @@
         <v>18</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>18</v>
@@ -1764,15 +1744,15 @@
         <v>18</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
@@ -1793,10 +1773,10 @@
         <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -1805,15 +1785,15 @@
         <v>18</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>14</v>
@@ -1834,10 +1814,10 @@
         <v>18</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>18</v>
@@ -1846,15 +1826,15 @@
         <v>18</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
@@ -1875,10 +1855,10 @@
         <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
@@ -1887,15 +1867,15 @@
         <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>14</v>
@@ -1916,7 +1896,7 @@
         <v>18</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I7" s="7">
         <v>90210</v>
@@ -1928,10 +1908,10 @@
         <v>18</v>
       </c>
       <c r="L7" s="24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1951,7 +1931,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>14</v>
@@ -1972,7 +1952,7 @@
         <v>17</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2">
         <v>5001</v>
@@ -1984,15 +1964,15 @@
         <v>18</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>14</v>
@@ -2013,7 +1993,7 @@
         <v>18</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I10" s="12">
         <v>4111111111111110</v>
@@ -2025,15 +2005,15 @@
         <v>18</v>
       </c>
       <c r="L10" s="24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M10" s="24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2054,7 +2034,7 @@
         <v>18</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I11" s="13">
         <v>46752</v>
@@ -2066,15 +2046,15 @@
         <v>18</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M11" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>14</v>
@@ -2095,7 +2075,7 @@
         <v>18</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I12" s="7">
         <v>1001</v>
@@ -2130,7 +2110,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>32</v>
@@ -2151,7 +2131,7 @@
         <v>17</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I14" s="2">
         <v>2001</v>
@@ -2163,15 +2143,15 @@
         <v>18</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>32</v>
@@ -2192,7 +2172,7 @@
         <v>18</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I15" s="7">
         <v>1001</v>
@@ -2212,7 +2192,7 @@
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>32</v>
@@ -2233,7 +2213,7 @@
         <v>18</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I16" s="2">
         <v>3001</v>
@@ -2245,15 +2225,15 @@
         <v>18</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M16" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>32</v>
@@ -2274,10 +2254,10 @@
         <v>18</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>18</v>
@@ -2286,15 +2266,15 @@
         <v>18</v>
       </c>
       <c r="L17" s="24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>32</v>
@@ -2315,10 +2295,10 @@
         <v>18</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>18</v>
@@ -2327,15 +2307,15 @@
         <v>18</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>32</v>
@@ -2356,10 +2336,10 @@
         <v>18</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>18</v>
@@ -2368,15 +2348,15 @@
         <v>18</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>32</v>
@@ -2397,10 +2377,10 @@
         <v>18</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>18</v>
@@ -2409,15 +2389,15 @@
         <v>18</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>32</v>
@@ -2438,7 +2418,7 @@
         <v>18</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I21" s="7">
         <v>10</v>
@@ -2450,15 +2430,15 @@
         <v>18</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>32</v>
@@ -2479,10 +2459,10 @@
         <v>18</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>18</v>
@@ -2491,15 +2471,15 @@
         <v>18</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>32</v>
@@ -2520,7 +2500,7 @@
         <v>18</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I23" s="20">
         <v>250</v>
@@ -2532,15 +2512,15 @@
         <v>18</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
@@ -2561,10 +2541,10 @@
         <v>18</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>18</v>
@@ -2573,15 +2553,15 @@
         <v>18</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>32</v>
@@ -2602,7 +2582,7 @@
         <v>18</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I25" s="22">
         <v>46037</v>
@@ -2614,15 +2594,15 @@
         <v>18</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>32</v>
@@ -2643,7 +2623,7 @@
         <v>18</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I26" s="13">
         <v>46068</v>
@@ -2655,10 +2635,10 @@
         <v>18</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2678,7 +2658,7 @@
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>51</v>
@@ -2699,7 +2679,7 @@
         <v>17</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I28" s="7">
         <v>4001</v>
@@ -2711,15 +2691,15 @@
         <v>18</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>51</v>
@@ -2740,7 +2720,7 @@
         <v>18</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I29" s="2">
         <v>1002</v>
@@ -2760,7 +2740,7 @@
     </row>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>51</v>
@@ -2781,7 +2761,7 @@
         <v>18</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I30" s="7">
         <v>5001</v>
@@ -2801,7 +2781,7 @@
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>51</v>
@@ -2822,7 +2802,7 @@
         <v>18</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I31" s="2">
         <v>12.99</v>
@@ -2834,15 +2814,15 @@
         <v>18</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>51</v>
@@ -2863,7 +2843,7 @@
         <v>18</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I32" s="7">
         <v>8</v>
@@ -2875,15 +2855,15 @@
         <v>18</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>51</v>
@@ -2904,7 +2884,7 @@
         <v>18</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I33" s="23">
         <v>275.5</v>
@@ -2916,15 +2896,15 @@
         <v>18</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>51</v>
@@ -2945,10 +2925,10 @@
         <v>18</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>18</v>
@@ -2957,15 +2937,15 @@
         <v>18</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>51</v>
@@ -2986,7 +2966,7 @@
         <v>18</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I35" s="2">
         <v>10001</v>
@@ -2998,15 +2978,15 @@
         <v>18</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>51</v>
@@ -3027,10 +3007,10 @@
         <v>18</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>18</v>
@@ -3039,15 +3019,15 @@
         <v>18</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>51</v>
@@ -3068,10 +3048,10 @@
         <v>18</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>18</v>
@@ -3080,10 +3060,10 @@
         <v>18</v>
       </c>
       <c r="L37" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -3103,7 +3083,7 @@
     </row>
     <row r="39" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>51</v>
@@ -3124,7 +3104,7 @@
         <v>18</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I39" s="7">
         <v>4001</v>
@@ -3144,7 +3124,7 @@
     </row>
     <row r="40" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>51</v>
@@ -3165,7 +3145,7 @@
         <v>18</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I40" s="2">
         <v>2001</v>
@@ -3185,7 +3165,7 @@
     </row>
     <row r="41" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>51</v>
@@ -3206,7 +3186,7 @@
         <v>18</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I41" s="20">
         <v>240</v>
@@ -3218,10 +3198,10 @@
         <v>18</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -3241,7 +3221,7 @@
     </row>
     <row r="43" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>51</v>
@@ -3262,7 +3242,7 @@
         <v>17</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I43" s="2">
         <v>7001</v>
@@ -3274,15 +3254,15 @@
         <v>18</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>51</v>
@@ -3303,7 +3283,7 @@
         <v>18</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I44" s="7">
         <v>4001</v>
@@ -3323,7 +3303,7 @@
     </row>
     <row r="45" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>51</v>
@@ -3344,10 +3324,10 @@
         <v>18</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>18</v>
@@ -3356,15 +3336,15 @@
         <v>18</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>51</v>
@@ -3385,10 +3365,10 @@
         <v>18</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>18</v>
@@ -3397,15 +3377,15 @@
         <v>18</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>51</v>
@@ -3426,7 +3406,7 @@
         <v>18</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="I47" s="13">
         <v>46038</v>
@@ -3438,10 +3418,10 @@
         <v>18</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -3461,7 +3441,7 @@
     </row>
     <row r="49" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>74</v>
@@ -3482,7 +3462,7 @@
         <v>17</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I49" s="7">
         <v>3001</v>
@@ -3502,7 +3482,7 @@
     </row>
     <row r="50" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>74</v>
@@ -3523,10 +3503,10 @@
         <v>18</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>18</v>
@@ -3535,15 +3515,15 @@
         <v>18</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>74</v>
@@ -3564,7 +3544,7 @@
         <v>18</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I51" s="7">
         <v>1001</v>
@@ -3584,7 +3564,7 @@
     </row>
     <row r="52" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>74</v>
@@ -3605,10 +3585,10 @@
         <v>18</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>18</v>
@@ -3617,15 +3597,15 @@
         <v>18</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>74</v>
@@ -3646,10 +3626,10 @@
         <v>18</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J53" s="7" t="s">
         <v>18</v>
@@ -3658,15 +3638,15 @@
         <v>18</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>74</v>
@@ -3687,10 +3667,10 @@
         <v>18</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>18</v>
@@ -3699,15 +3679,15 @@
         <v>18</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>74</v>
@@ -3728,7 +3708,7 @@
         <v>18</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I55" s="7">
         <v>10</v>
@@ -3740,15 +3720,15 @@
         <v>18</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>74</v>
@@ -3769,10 +3749,10 @@
         <v>18</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>18</v>
@@ -3781,15 +3761,15 @@
         <v>18</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>74</v>
@@ -3810,10 +3790,10 @@
         <v>18</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J57" s="7" t="s">
         <v>18</v>
@@ -3822,15 +3802,15 @@
         <v>18</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>74</v>
@@ -3851,10 +3831,10 @@
         <v>18</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I58" s="21" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>18</v>
@@ -3863,15 +3843,15 @@
         <v>18</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>74</v>
@@ -3892,7 +3872,7 @@
         <v>18</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I59" s="22">
         <v>46032</v>
@@ -3904,10 +3884,10 @@
         <v>18</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -3927,7 +3907,7 @@
     </row>
     <row r="61" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>84</v>
@@ -3948,7 +3928,7 @@
         <v>17</v>
       </c>
       <c r="H61" s="21" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I61" s="2">
         <v>9001</v>
@@ -3960,15 +3940,15 @@
         <v>18</v>
       </c>
       <c r="L61" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>84</v>
@@ -3989,7 +3969,7 @@
         <v>18</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="I62" s="7">
         <v>1002</v>
@@ -4009,7 +3989,7 @@
     </row>
     <row r="63" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>84</v>
@@ -4030,10 +4010,10 @@
         <v>18</v>
       </c>
       <c r="H63" s="21" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>18</v>
@@ -4042,15 +4022,15 @@
         <v>18</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>84</v>
@@ -4071,10 +4051,10 @@
         <v>18</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J64" s="7" t="s">
         <v>18</v>
@@ -4083,15 +4063,15 @@
         <v>18</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>84</v>
@@ -4112,10 +4092,10 @@
         <v>18</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>18</v>
@@ -4124,15 +4104,15 @@
         <v>18</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>84</v>
@@ -4153,10 +4133,10 @@
         <v>18</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="J66" s="7" t="s">
         <v>18</v>
@@ -4165,15 +4145,15 @@
         <v>18</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>84</v>
@@ -4194,10 +4174,10 @@
         <v>18</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>18</v>
@@ -4206,15 +4186,15 @@
         <v>18</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>84</v>
@@ -4235,7 +4215,7 @@
         <v>18</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I68" s="7">
         <v>4001</v>
@@ -4255,7 +4235,7 @@
     </row>
     <row r="69" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>84</v>
@@ -4276,10 +4256,10 @@
         <v>18</v>
       </c>
       <c r="H69" s="21" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>18</v>
@@ -4288,15 +4268,15 @@
         <v>18</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>84</v>
@@ -4317,7 +4297,7 @@
         <v>18</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I70" s="24" t="s">
         <v>21</v>
@@ -4329,10 +4309,10 @@
         <v>18</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -10954,7 +10934,7 @@
         <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10974,7 +10954,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10988,13 +10968,13 @@
         <v>102</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>103</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11014,7 +10994,7 @@
         <v>99</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11034,7 +11014,7 @@
         <v>99</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11054,7 +11034,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11068,13 +11048,13 @@
         <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11094,7 +11074,7 @@
         <v>99</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -15068,7 +15048,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>115</v>
       </c>
@@ -15079,60 +15059,60 @@
         <v>13</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>245</v>
+        <v>221</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>239</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="J2" s="27" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>115</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>246</v>
+        <v>226</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>240</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>115</v>
       </c>
@@ -15143,30 +15123,30 @@
         <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F4" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="28" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J4" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>21</v>
@@ -15175,25 +15155,25 @@
         <v>13</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="I5" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>244</v>
+      <c r="J5" s="27" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -15243,18 +15223,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>121</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
@@ -15325,25 +15297,19 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>127</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
